--- a/xlsx/cards-pages/cards.search.xlsx
+++ b/xlsx/cards-pages/cards.search.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="481">
   <si>
     <t>row_seq</t>
   </si>
@@ -1347,6 +1347,129 @@
   </si>
   <si>
     <t>https://www.zhoublog.cn/</t>
+  </si>
+  <si>
+    <t>envato</t>
+  </si>
+  <si>
+    <t>https://elements.envato.com/graphics/icons</t>
+  </si>
+  <si>
+    <t>Google analytics</t>
+  </si>
+  <si>
+    <t>谷歌统计</t>
+  </si>
+  <si>
+    <t>https://analytics.google.com/analytics/web/</t>
+  </si>
+  <si>
+    <t>bootstrap</t>
+  </si>
+  <si>
+    <t>Html模板库</t>
+  </si>
+  <si>
+    <t>https://www.bootstrapmb.com/item/16724</t>
+  </si>
+  <si>
+    <t>收取的违约金、罚款等，​应当开具发票、不得开具发票的情形​？v</t>
+  </si>
+  <si>
+    <t>https://www.sohu.com/a/780833460_467122</t>
+  </si>
+  <si>
+    <t>网易163邮箱</t>
+  </si>
+  <si>
+    <t>https://email.163.com/</t>
+  </si>
+  <si>
+    <t>2025年度中级会计专业技术资格考试大纲</t>
+  </si>
+  <si>
+    <t>https://kjs.mof.gov.cn/zhengcefabu/202504/t20250411_3961852.htm</t>
+  </si>
+  <si>
+    <t>自然人电子税务局</t>
+  </si>
+  <si>
+    <t>https://etax.chinatax.gov.cn/</t>
+  </si>
+  <si>
+    <t>工商银行（泰国）</t>
+  </si>
+  <si>
+    <t>https://corpebank.icbc.com.cn/icbc/corporbank/index.jsp?areaCode=0165&amp;dse_locale=zh-CN</t>
+  </si>
+  <si>
+    <t>微信读书</t>
+  </si>
+  <si>
+    <t>https://weread.qq.com/</t>
+  </si>
+  <si>
+    <t>哈佛大学公开课</t>
+  </si>
+  <si>
+    <t>https://pll.harvard.edu/catalog</t>
+  </si>
+  <si>
+    <t>微信公众平台</t>
+  </si>
+  <si>
+    <t>公众号登录</t>
+  </si>
+  <si>
+    <t>https://mp.weixin.qq.com/cgi-bin/loginpage</t>
+  </si>
+  <si>
+    <t>13张图搞定身体动作、姿势常用英语口语表达！（附22类肢体动作英文表达）</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/447475913</t>
+  </si>
+  <si>
+    <t>注册会计师全国统一考试网上报名</t>
+  </si>
+  <si>
+    <t>https://cpaexam.cicpa.org.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>https://cpaexam.cicpa.org.cn/</t>
+  </si>
+  <si>
+    <t>Google 云端硬盘</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/home</t>
+  </si>
+  <si>
+    <t>百度统计</t>
+  </si>
+  <si>
+    <t>https://tongji.baidu.com/web5/welcome/login</t>
+  </si>
+  <si>
+    <t>中国人民银行征信中心</t>
+  </si>
+  <si>
+    <t>征信报告，个人信用信息服务平台</t>
+  </si>
+  <si>
+    <t>https://ipcrs.pbccrc.org.cn/</t>
+  </si>
+  <si>
+    <t>Google 搜索分析</t>
+  </si>
+  <si>
+    <t>https://search.google.com/search-console</t>
+  </si>
+  <si>
+    <t>Google AdSense 广告联盟</t>
+  </si>
+  <si>
+    <t>https://adsense.google.com</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1482,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1373,13 +1496,6 @@
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1822,28 +1938,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1852,123 +1971,121 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2316,7 +2433,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG86"/>
+  <dimension ref="A1:AG100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="14" max="31" width="1.375" customWidth="1"/>
@@ -4823,8 +4940,17 @@
       <c r="E78">
         <v>1</v>
       </c>
+      <c r="F78" t="s">
+        <v>440</v>
+      </c>
+      <c r="G78" t="s">
+        <v>422</v>
+      </c>
       <c r="L78" t="s">
         <v>411</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>441</v>
       </c>
       <c r="AF78" t="s">
         <v>41</v>
@@ -4843,8 +4969,20 @@
       <c r="E79">
         <v>1</v>
       </c>
+      <c r="F79" t="s">
+        <v>442</v>
+      </c>
+      <c r="G79" t="s">
+        <v>443</v>
+      </c>
+      <c r="I79" t="s">
+        <v>410</v>
+      </c>
       <c r="L79" t="s">
         <v>411</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="AF79" t="s">
         <v>41</v>
@@ -4863,8 +5001,17 @@
       <c r="E80">
         <v>1</v>
       </c>
+      <c r="F80" t="s">
+        <v>445</v>
+      </c>
+      <c r="G80" t="s">
+        <v>446</v>
+      </c>
       <c r="L80" t="s">
         <v>411</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>447</v>
       </c>
       <c r="AF80" t="s">
         <v>41</v>
@@ -4883,8 +5030,14 @@
       <c r="E81">
         <v>1</v>
       </c>
+      <c r="F81" t="s">
+        <v>448</v>
+      </c>
       <c r="L81" t="s">
         <v>411</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>449</v>
       </c>
       <c r="AF81" t="s">
         <v>41</v>
@@ -4903,8 +5056,14 @@
       <c r="E82">
         <v>1</v>
       </c>
+      <c r="F82" t="s">
+        <v>450</v>
+      </c>
       <c r="L82" t="s">
         <v>411</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>451</v>
       </c>
       <c r="AF82" t="s">
         <v>41</v>
@@ -4923,8 +5082,14 @@
       <c r="E83">
         <v>1</v>
       </c>
+      <c r="F83" t="s">
+        <v>452</v>
+      </c>
       <c r="L83" t="s">
         <v>411</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>453</v>
       </c>
       <c r="AF83" t="s">
         <v>41</v>
@@ -4943,8 +5108,14 @@
       <c r="E84">
         <v>1</v>
       </c>
+      <c r="F84" t="s">
+        <v>454</v>
+      </c>
       <c r="L84" t="s">
         <v>411</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>455</v>
       </c>
       <c r="AF84" t="s">
         <v>41</v>
@@ -4963,8 +5134,14 @@
       <c r="E85">
         <v>1</v>
       </c>
+      <c r="F85" t="s">
+        <v>456</v>
+      </c>
       <c r="L85" t="s">
         <v>411</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>457</v>
       </c>
       <c r="AF85" t="s">
         <v>41</v>
@@ -4983,10 +5160,359 @@
       <c r="E86">
         <v>1</v>
       </c>
+      <c r="F86" t="s">
+        <v>458</v>
+      </c>
       <c r="L86" t="s">
         <v>411</v>
       </c>
+      <c r="M86" s="2" t="s">
+        <v>459</v>
+      </c>
       <c r="AF86" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="87" spans="1:32">
+      <c r="A87" t="s">
+        <v>437</v>
+      </c>
+      <c r="B87" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" t="s">
+        <v>408</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87" t="s">
+        <v>460</v>
+      </c>
+      <c r="L87" t="s">
+        <v>411</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="AF87" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:32">
+      <c r="A88" t="s">
+        <v>437</v>
+      </c>
+      <c r="B88" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" t="s">
+        <v>408</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>462</v>
+      </c>
+      <c r="G88" t="s">
+        <v>463</v>
+      </c>
+      <c r="L88" t="s">
+        <v>411</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="AF88" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="89" spans="1:32">
+      <c r="A89" t="s">
+        <v>437</v>
+      </c>
+      <c r="B89" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" t="s">
+        <v>408</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89" t="s">
+        <v>465</v>
+      </c>
+      <c r="L89" t="s">
+        <v>411</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="AF89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="90" spans="1:32">
+      <c r="A90" t="s">
+        <v>437</v>
+      </c>
+      <c r="B90" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" t="s">
+        <v>408</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>467</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="L90" t="s">
+        <v>411</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="AF90" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="91" spans="1:32">
+      <c r="A91" t="s">
+        <v>437</v>
+      </c>
+      <c r="B91" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" t="s">
+        <v>408</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91" t="s">
+        <v>470</v>
+      </c>
+      <c r="L91" t="s">
+        <v>411</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="AF91" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="92" spans="1:32">
+      <c r="A92" t="s">
+        <v>437</v>
+      </c>
+      <c r="B92" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" t="s">
+        <v>408</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92" t="s">
+        <v>472</v>
+      </c>
+      <c r="L92" t="s">
+        <v>411</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="AF92" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="93" spans="1:32">
+      <c r="A93" t="s">
+        <v>437</v>
+      </c>
+      <c r="B93" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" t="s">
+        <v>408</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93" t="s">
+        <v>474</v>
+      </c>
+      <c r="G93" t="s">
+        <v>475</v>
+      </c>
+      <c r="L93" t="s">
+        <v>411</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="AF93" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="94" spans="1:32">
+      <c r="A94" t="s">
+        <v>437</v>
+      </c>
+      <c r="B94" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" t="s">
+        <v>408</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>477</v>
+      </c>
+      <c r="L94" t="s">
+        <v>411</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="AF94" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="95" spans="1:32">
+      <c r="A95" t="s">
+        <v>437</v>
+      </c>
+      <c r="B95" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" t="s">
+        <v>408</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>479</v>
+      </c>
+      <c r="L95" t="s">
+        <v>411</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="AF95" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="96" spans="1:32">
+      <c r="A96" t="s">
+        <v>437</v>
+      </c>
+      <c r="B96" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" t="s">
+        <v>408</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="L96" t="s">
+        <v>411</v>
+      </c>
+      <c r="AF96" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="97" spans="1:32">
+      <c r="A97" t="s">
+        <v>437</v>
+      </c>
+      <c r="B97" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" t="s">
+        <v>408</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="L97" t="s">
+        <v>411</v>
+      </c>
+      <c r="AF97" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" spans="1:32">
+      <c r="A98" t="s">
+        <v>437</v>
+      </c>
+      <c r="B98" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" t="s">
+        <v>408</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="L98" t="s">
+        <v>411</v>
+      </c>
+      <c r="AF98" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="99" spans="1:32">
+      <c r="A99" t="s">
+        <v>437</v>
+      </c>
+      <c r="B99" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" t="s">
+        <v>408</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="L99" t="s">
+        <v>411</v>
+      </c>
+      <c r="AF99" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" spans="1:32">
+      <c r="A100" t="s">
+        <v>437</v>
+      </c>
+      <c r="B100" t="s">
+        <v>34</v>
+      </c>
+      <c r="D100" t="s">
+        <v>408</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="L100" t="s">
+        <v>411</v>
+      </c>
+      <c r="AF100" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5002,6 +5528,25 @@
     <hyperlink ref="M75" r:id="rId7" display="https://wenku.baidu.com/"/>
     <hyperlink ref="M76" r:id="rId8" display="https://www.runoob.com/"/>
     <hyperlink ref="M77" r:id="rId9" display="https://www.zhoublog.cn/"/>
+    <hyperlink ref="M78" r:id="rId10" display="https://elements.envato.com/graphics/icons"/>
+    <hyperlink ref="M79" r:id="rId11" display="https://analytics.google.com/analytics/web/"/>
+    <hyperlink ref="M80" r:id="rId12" display="https://www.bootstrapmb.com/item/16724"/>
+    <hyperlink ref="M81" r:id="rId13" display="https://www.sohu.com/a/780833460_467122"/>
+    <hyperlink ref="M82" r:id="rId14" display="https://email.163.com/"/>
+    <hyperlink ref="M83" r:id="rId15" display="https://kjs.mof.gov.cn/zhengcefabu/202504/t20250411_3961852.htm"/>
+    <hyperlink ref="M84" r:id="rId16" display="https://etax.chinatax.gov.cn/"/>
+    <hyperlink ref="M85" r:id="rId17" display="https://corpebank.icbc.com.cn/icbc/corporbank/index.jsp?areaCode=0165&amp;dse_locale=zh-CN"/>
+    <hyperlink ref="M86" r:id="rId18" display="https://weread.qq.com/"/>
+    <hyperlink ref="M87" r:id="rId19" display="https://pll.harvard.edu/catalog"/>
+    <hyperlink ref="M88" r:id="rId20" display="https://mp.weixin.qq.com/cgi-bin/loginpage"/>
+    <hyperlink ref="M89" r:id="rId21" display="https://zhuanlan.zhihu.com/p/447475913"/>
+    <hyperlink ref="M90" r:id="rId22" display="https://cpaexam.cicpa.org.cn/"/>
+    <hyperlink ref="H90" r:id="rId23" display="https://cpaexam.cicpa.org.cn/favicon.ico"/>
+    <hyperlink ref="M91" r:id="rId24" display="https://drive.google.com/drive/home"/>
+    <hyperlink ref="M92" r:id="rId25" display="https://tongji.baidu.com/web5/welcome/login"/>
+    <hyperlink ref="M93" r:id="rId26" display="https://ipcrs.pbccrc.org.cn/"/>
+    <hyperlink ref="M94" r:id="rId27" display="https://search.google.com/search-console"/>
+    <hyperlink ref="M95" r:id="rId28" display="https://adsense.google.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
